--- a/data/trans_orig/IQ21C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Provincia-trans_orig.xlsx
@@ -12731,7 +12731,7 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -13064,7 +13064,7 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="W114" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -25640,7 +25640,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
@@ -25690,7 +25690,7 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -25786,7 +25786,7 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -26049,7 +26049,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -26064,7 +26064,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -26099,7 +26099,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -26190,12 +26190,12 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -26205,12 +26205,12 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -26225,12 +26225,12 @@
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
@@ -26240,12 +26240,12 @@
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -26306,7 +26306,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="W114" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -26619,7 +26619,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -26654,7 +26654,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -26689,7 +26689,7 @@
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -26730,7 +26730,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -26785,7 +26785,7 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -26826,7 +26826,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -26841,7 +26841,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -26876,7 +26876,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="W119" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -39028,7 +39028,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -39043,7 +39043,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -39063,7 +39063,7 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -39078,7 +39078,7 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -39104,7 +39104,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -39119,7 +39119,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -39174,7 +39174,7 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -39189,7 +39189,7 @@
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -39215,7 +39215,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -39230,7 +39230,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -39285,7 +39285,7 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -39300,7 +39300,7 @@
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -39361,7 +39361,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -39376,7 +39376,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -39396,7 +39396,7 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
@@ -39411,7 +39411,7 @@
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -39437,7 +39437,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -39452,7 +39452,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -39507,7 +39507,7 @@
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
@@ -39522,7 +39522,7 @@
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -39770,7 +39770,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -39785,7 +39785,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -39805,7 +39805,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -39820,7 +39820,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -39840,7 +39840,7 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
@@ -39855,7 +39855,7 @@
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -39881,7 +39881,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -39896,7 +39896,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -39951,7 +39951,7 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -39966,7 +39966,7 @@
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -39992,7 +39992,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -40007,7 +40007,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -40027,7 +40027,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -40042,7 +40042,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -40057,12 +40057,12 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -40072,12 +40072,12 @@
       </c>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -40138,7 +40138,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -40173,7 +40173,7 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="W119" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -53339,7 +53339,7 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -53354,7 +53354,7 @@
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
